--- a/artfynd/A 7955-2022 artfynd.xlsx
+++ b/artfynd/A 7955-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7955-2022 artfynd.xlsx
+++ b/artfynd/A 7955-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112027055</v>
+        <v>112027083</v>
       </c>
       <c r="B2" t="n">
-        <v>81386</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>817165</v>
+        <v>817185</v>
       </c>
       <c r="R2" t="n">
-        <v>7526150</v>
+        <v>7526110</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -788,12 +783,7 @@
         <v>112027025</v>
       </c>
       <c r="B3" t="n">
-        <v>89554</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112027073</v>
+        <v>112027081</v>
       </c>
       <c r="B4" t="n">
-        <v>89572</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>817105</v>
+        <v>817185</v>
       </c>
       <c r="R4" t="n">
-        <v>7526180</v>
+        <v>7526110</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112027081</v>
+        <v>112027015</v>
       </c>
       <c r="B5" t="n">
-        <v>89554</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>817185</v>
+        <v>817280</v>
       </c>
       <c r="R5" t="n">
-        <v>7526110</v>
+        <v>7525960</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,15 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112027015</v>
+        <v>112027055</v>
       </c>
       <c r="B6" t="n">
-        <v>81386</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>817280</v>
+        <v>817165</v>
       </c>
       <c r="R6" t="n">
-        <v>7525960</v>
+        <v>7526150</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,226 +1197,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112027020</v>
-      </c>
-      <c r="B7" t="n">
-        <v>89572</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Oksajärvi, Nb</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>817295</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7526150</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Junosuando</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>112027083</v>
-      </c>
-      <c r="B8" t="n">
-        <v>89835</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>658</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Oksajärvi, Nb</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>817185</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7526110</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Junosuando</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7955-2022 artfynd.xlsx
+++ b/artfynd/A 7955-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112027083</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112027025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112027081</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112027015</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,8 +1222,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112027055</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>